--- a/reports/FR-17_boundary_test_cases.xlsx
+++ b/reports/FR-17_boundary_test_cases.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variables!$A$1:$E$10</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
